--- a/docs/cet200_spec.xlsx
+++ b/docs/cet200_spec.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F31177C-01FD-4AD5-88F9-10757F4EDB0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C7426E-A3D2-462E-B8C4-34C0C46F5052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="3" xr2:uid="{3844978D-FC62-4D1C-9D18-961F59752572}"/>
+    <workbookView xWindow="28680" yWindow="-5475" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{3844978D-FC62-4D1C-9D18-961F59752572}"/>
   </bookViews>
   <sheets>
     <sheet name="基本スペック" sheetId="3" r:id="rId1"/>
@@ -333,13 +333,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>グローバル座標[-1906.75, 0, 1560]</t>
-    <rPh sb="5" eb="7">
-      <t>ザヒョウ</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>ブームからバケットまでの合計質量</t>
     <rPh sb="12" eb="14">
       <t>ゴウケイ</t>
@@ -773,16 +766,6 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>重心自動計算</t>
-    <rPh sb="0" eb="2">
-      <t>ジュウシン</t>
-    </rPh>
-    <rPh sb="2" eb="6">
-      <t>ジドウケイサン</t>
-    </rPh>
-    <phoneticPr fontId="18"/>
-  </si>
-  <si>
     <t>重心オフセット</t>
     <rPh sb="0" eb="2">
       <t>ジュウシン</t>
@@ -837,9 +820,6 @@
     <t>[ 1.0987, 0, 0; 0, 3.5308, 0; 0, 0, 3.9491 ] kg·m²</t>
   </si>
   <si>
-    <t>[ 5395.4, -512.7, -335.58; -512.7, 10231, -88.36; -335.58, -88.36, 13848 ] kg·m²</t>
-  </si>
-  <si>
     <t>[ 2289.8, 0, 0; 0, 2862.6, 0; 0, 0, 4858.4 ] kg·m²</t>
   </si>
   <si>
@@ -1173,6 +1153,33 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>スイリョク</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>[ 5408.8, -510.88, -373.21; -510.88, 10238, -98.271; -373.21, -98.271, 13840 ] kg·m²</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>非オフセット時の重心</t>
+    <rPh sb="0" eb="1">
+      <t>ヒ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ジュウシン</t>
+    </rPh>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>新重心</t>
+    <rPh sb="0" eb="1">
+      <t>シン</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>ジュウシン</t>
     </rPh>
     <phoneticPr fontId="18"/>
   </si>
@@ -2241,131 +2248,131 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A1" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2">
         <v>5.5</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D2">
         <f>B2/3.6</f>
         <v>1.5277777777777777</v>
       </c>
       <c r="E2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D3">
         <f>D2/B29</f>
         <v>4.0741044940542963</v>
       </c>
       <c r="E3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4">
         <v>205</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D4">
         <f>B4*1000</f>
         <v>205000</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D5">
         <f>D4*B29/2</f>
         <v>38437.212999999996</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6">
         <f>B6/60*2*PI()</f>
         <v>1.2566370614359172</v>
       </c>
       <c r="E6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B7">
         <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B8">
         <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A12" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>0.8</v>
@@ -2373,7 +2380,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <f>B15*B16</f>
@@ -2382,7 +2389,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B15">
         <v>0.6111307574999999</v>
@@ -2390,7 +2397,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>0.99</v>
@@ -2398,7 +2405,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B17">
         <v>1.1299999999999999</v>
@@ -2406,7 +2413,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B18">
         <v>1.07</v>
@@ -2414,7 +2421,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19">
         <v>0.21157000000000001</v>
@@ -2422,7 +2429,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20">
         <v>0.1</v>
@@ -2430,7 +2437,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21">
         <v>7.4075299999999997E-2</v>
@@ -2438,7 +2445,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B22">
         <v>0.01</v>
@@ -2446,12 +2453,12 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A25" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B26">
         <v>2</v>
@@ -2459,7 +2466,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B27">
         <v>7</v>
@@ -2467,7 +2474,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28">
         <v>46</v>
@@ -2475,7 +2482,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B29">
         <v>0.37499719999999997</v>
@@ -2483,27 +2490,27 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" t="s">
+        <v>125</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
         <v>124</v>
-      </c>
-      <c r="B31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" t="s">
-        <v>125</v>
-      </c>
-      <c r="D31" t="s">
-        <v>126</v>
-      </c>
-      <c r="E31" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B32" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C32">
         <v>168</v>
@@ -2517,10 +2524,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C33">
         <v>255</v>
@@ -2534,10 +2541,10 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B34" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C34">
         <v>255</v>
@@ -2551,10 +2558,10 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C35">
         <v>234</v>
@@ -2590,26 +2597,26 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="B1" s="10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" s="6" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B3" s="10">
         <v>1E-8</v>
@@ -2624,7 +2631,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B4" s="10">
         <v>1E-8</v>
@@ -2639,7 +2646,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B5" s="10">
         <f>2/60</f>
@@ -2661,14 +2668,14 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G7" s="10"/>
       <c r="H7" s="10"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B8" s="10">
         <f>1/B3</f>
@@ -2686,7 +2693,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B9" s="10">
         <f>1/B4</f>
@@ -2704,14 +2711,14 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="G10" s="10"/>
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="B11" s="10">
         <f>B8*B5</f>
@@ -2729,7 +2736,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="B12" s="10">
         <f>B9*B5</f>
@@ -2751,21 +2758,21 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" s="6" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="G15" s="10"/>
       <c r="H15" s="10"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B16" s="10">
         <f>B8/$B$24</f>
@@ -2794,7 +2801,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B17" s="10">
         <f>B9*$B$25</f>
@@ -2823,7 +2830,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" s="6" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F18" s="10"/>
       <c r="G18" s="10"/>
@@ -2831,7 +2838,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="B19" s="10">
         <f>B11/$B$24</f>
@@ -2860,7 +2867,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B20" s="10">
         <f>B12*$B$25</f>
@@ -2897,14 +2904,14 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" s="6" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B24" s="10">
         <v>1000</v>
@@ -2914,7 +2921,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B25" s="10">
         <f>PI()/180</f>
@@ -2925,27 +2932,27 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" s="6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -2994,24 +3001,24 @@
         <v>38</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>105</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="Q1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A2" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="2">
@@ -3031,40 +3038,40 @@
         <v>39</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="I2" s="2"/>
       <c r="K2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L2" t="s">
         <v>102</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>103</v>
       </c>
-      <c r="M2" t="s">
-        <v>104</v>
-      </c>
       <c r="N2" t="s">
+        <v>101</v>
+      </c>
+      <c r="O2" t="s">
         <v>102</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>103</v>
       </c>
-      <c r="P2" t="s">
-        <v>104</v>
-      </c>
       <c r="Q2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R2" t="s">
         <v>102</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>103</v>
-      </c>
-      <c r="S2" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A3" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3">
@@ -3078,13 +3085,13 @@
         <v>7600</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>39</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>35</v>
@@ -3096,7 +3103,7 @@
         <v>1.25</v>
       </c>
       <c r="M3">
-        <v>1598.04</v>
+        <v>1608.04</v>
       </c>
       <c r="N3">
         <v>-1906.75</v>
@@ -3117,12 +3124,12 @@
       </c>
       <c r="S3">
         <f>P3-M3</f>
-        <v>-38.039999999999964</v>
+        <v>-48.039999999999964</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="2">
@@ -3142,13 +3149,13 @@
         <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="I4" s="2"/>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A5" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="2">
@@ -3168,13 +3175,13 @@
         <v>39</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I5" s="2"/>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A6" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="2">
@@ -3194,13 +3201,13 @@
         <v>39</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="2">
@@ -3220,13 +3227,13 @@
         <v>39</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A8" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="2">
@@ -3246,7 +3253,7 @@
         <v>39</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>32</v>
@@ -3254,7 +3261,7 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B9" s="4"/>
       <c r="C9" s="2">
@@ -3274,7 +3281,7 @@
         <v>39</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>33</v>
@@ -3282,7 +3289,7 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="2">
@@ -3302,7 +3309,7 @@
         <v>39</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>34</v>
@@ -3310,7 +3317,7 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="2">
@@ -3330,13 +3337,13 @@
         <v>39</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A12" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="2">
@@ -3356,15 +3363,15 @@
         <v>39</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="2">
@@ -3384,13 +3391,13 @@
         <v>39</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A14" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="2">
@@ -3410,13 +3417,13 @@
         <v>39</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="I14" s="2"/>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="2">
@@ -3436,13 +3443,13 @@
         <v>39</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.4">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="2">
@@ -3462,13 +3469,13 @@
         <v>39</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A17" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B17" s="4"/>
       <c r="C17" s="2">
@@ -3488,15 +3495,15 @@
         <v>39</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="2">
@@ -3516,13 +3523,13 @@
         <v>39</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A19" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="2"/>
@@ -3599,7 +3606,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <f>SUM(E8:E18)</f>
@@ -3608,7 +3615,7 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25">
         <f>E20+E21</f>
@@ -3617,7 +3624,7 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <f>C20+C21</f>
@@ -3626,7 +3633,7 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E27">
         <f>SUM(E2:E18)</f>
@@ -3779,7 +3786,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8">
         <f>PI()*POWER(B39,2)/4</f>
@@ -3796,7 +3803,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9">
         <f>B8-B10</f>
@@ -3813,7 +3820,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B10">
         <f>PI()*POWER(B38,2)/4</f>
@@ -3830,7 +3837,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B11">
         <v>35</v>
@@ -3838,7 +3845,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -3846,7 +3853,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B13">
         <v>440</v>
@@ -3856,12 +3863,12 @@
         <v>7.3333333333333332E-3</v>
       </c>
       <c r="D13" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B14">
         <f>$B$11*B8*2</f>
@@ -3878,7 +3885,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B15">
         <f>$B$11*B9*2</f>
@@ -3895,7 +3902,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B16">
         <f>$B$12*B8*2</f>
@@ -3912,7 +3919,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B17">
         <f>$B$12*B9*2</f>
@@ -3929,7 +3936,7 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20" s="7" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B20" s="7">
         <f>$C$13/(B8*0.000001)</f>
@@ -3946,7 +3953,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21" s="7" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B21" s="7">
         <f>B14-B17</f>
@@ -3963,7 +3970,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22" s="7" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B22" s="7">
         <f>B15-B16</f>
@@ -3980,7 +3987,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B23">
         <v>2.5754974000000002</v>
@@ -3994,7 +4001,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24" s="7" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B24" s="7">
         <f>B23*B21</f>
@@ -4011,7 +4018,7 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B28">
         <f>(B3-B2)</f>
@@ -4028,7 +4035,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B29">
         <f>(B4-B2)</f>
@@ -4045,7 +4052,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30" s="7" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B30" s="7">
         <f>B28</f>
@@ -4061,7 +4068,7 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31" s="7" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B31" s="7">
         <f>B29</f>

--- a/docs/cet200_spec.xlsx
+++ b/docs/cet200_spec.xlsx
@@ -3,15 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0C7426E-A3D2-462E-B8C4-34C0C46F5052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BF25D9C-9330-4578-9AFC-F632CC2CEF47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5475" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{3844978D-FC62-4D1C-9D18-961F59752572}"/>
+    <workbookView xWindow="28680" yWindow="-5475" windowWidth="51840" windowHeight="21120" xr2:uid="{3844978D-FC62-4D1C-9D18-961F59752572}"/>
   </bookViews>
   <sheets>
     <sheet name="基本スペック" sheetId="3" r:id="rId1"/>
-    <sheet name="ジョイント" sheetId="4" r:id="rId2"/>
-    <sheet name="質量、重心、慣性テンソル" sheetId="2" r:id="rId3"/>
-    <sheet name="シリンダスペック" sheetId="1" r:id="rId4"/>
+    <sheet name="質量、重心、慣性テンソル" sheetId="2" r:id="rId2"/>
+    <sheet name="シリンダスペック" sheetId="1" r:id="rId3"/>
+    <sheet name="ジョイント" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2581,391 +2581,6 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718BB7D2-AA6F-42B4-9400-D5B966AA08E0}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="1" max="1" width="20.75" customWidth="1"/>
-    <col min="2" max="2" width="22.125" style="10" customWidth="1"/>
-    <col min="3" max="3" width="24.375" style="10" customWidth="1"/>
-    <col min="4" max="4" width="6.5" style="10" customWidth="1"/>
-    <col min="5" max="5" width="24.375" style="10" customWidth="1"/>
-    <col min="6" max="6" width="23.875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="12.875" customWidth="1"/>
-    <col min="8" max="8" width="34" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="B1" s="10" t="s">
-        <v>167</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>164</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A2" s="6" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A3" t="s">
-        <v>154</v>
-      </c>
-      <c r="B3" s="10">
-        <v>1E-8</v>
-      </c>
-      <c r="E3" s="10">
-        <v>1E-10</v>
-      </c>
-      <c r="G3" s="10">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="H3" s="10"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A4" t="s">
-        <v>155</v>
-      </c>
-      <c r="B4" s="10">
-        <v>1E-8</v>
-      </c>
-      <c r="E4" s="10">
-        <v>1E-10</v>
-      </c>
-      <c r="G4" s="10">
-        <v>9.9999999999999994E-12</v>
-      </c>
-      <c r="H4" s="10"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A5" t="s">
-        <v>156</v>
-      </c>
-      <c r="B5" s="10">
-        <f>2/60</f>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="E5" s="10">
-        <f>2/60</f>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="G5" s="10">
-        <f>2/60</f>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="H5" s="10"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A7" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B8" s="10">
-        <f>1/B3</f>
-        <v>100000000</v>
-      </c>
-      <c r="E8" s="10">
-        <f>1/E3</f>
-        <v>10000000000</v>
-      </c>
-      <c r="G8" s="10">
-        <f>1/G3</f>
-        <v>100000000000</v>
-      </c>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A9" t="s">
-        <v>150</v>
-      </c>
-      <c r="B9" s="10">
-        <f>1/B4</f>
-        <v>100000000</v>
-      </c>
-      <c r="E9" s="10">
-        <f>1/E4</f>
-        <v>10000000000</v>
-      </c>
-      <c r="G9" s="10">
-        <f>1/G4</f>
-        <v>100000000000</v>
-      </c>
-      <c r="H9" s="10"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A10" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B11" s="10">
-        <f>B8*B5</f>
-        <v>3333333.3333333335</v>
-      </c>
-      <c r="E11" s="10">
-        <f>E8*E5</f>
-        <v>333333333.33333331</v>
-      </c>
-      <c r="G11" s="10">
-        <f>G8*G5</f>
-        <v>3333333333.3333335</v>
-      </c>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="10">
-        <f>B9*B5</f>
-        <v>3333333.3333333335</v>
-      </c>
-      <c r="E12" s="10">
-        <f>E9*E5</f>
-        <v>333333333.33333331</v>
-      </c>
-      <c r="G12" s="10">
-        <f>G9*G5</f>
-        <v>3333333333.3333335</v>
-      </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A14" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A15" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A16" t="s">
-        <v>160</v>
-      </c>
-      <c r="B16" s="10">
-        <f>B8/$B$24</f>
-        <v>100000</v>
-      </c>
-      <c r="C16" t="str">
-        <f>TEXT(B16,"0.000000E+00")&amp;" "&amp;$A$28</f>
-        <v>1.000000E+05 N/mm</v>
-      </c>
-      <c r="E16" s="10">
-        <f>E8/$B$24</f>
-        <v>10000000</v>
-      </c>
-      <c r="F16" t="str">
-        <f>TEXT(E16,"0.000000E+00")&amp;" "&amp;$A$28</f>
-        <v>1.000000E+07 N/mm</v>
-      </c>
-      <c r="G16" s="10">
-        <f>G8/$B$24</f>
-        <v>100000000</v>
-      </c>
-      <c r="H16" t="str">
-        <f>TEXT(G16,"0.000000E+00")&amp;" "&amp;$A$28</f>
-        <v>1.000000E+08 N/mm</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17" s="10">
-        <f>B9*$B$25</f>
-        <v>1745329.2519943295</v>
-      </c>
-      <c r="C17" s="10" t="str">
-        <f>TEXT(B17,"0.000000E+00")&amp;" "&amp;$A$29</f>
-        <v>1.745329E+06 Nm/°</v>
-      </c>
-      <c r="E17" s="10">
-        <f>E9*$B$25</f>
-        <v>174532925.19943297</v>
-      </c>
-      <c r="F17" s="10" t="str">
-        <f>TEXT(E17,"0.000000E+00")&amp;" "&amp;$A$29</f>
-        <v>1.745329E+08 Nm/°</v>
-      </c>
-      <c r="G17" s="10">
-        <f>G9*$B$25</f>
-        <v>1745329251.9943295</v>
-      </c>
-      <c r="H17" s="10" t="str">
-        <f>TEXT(G17,"0.000000E+00")&amp;" "&amp;$A$29</f>
-        <v>1.745329E+09 Nm/°</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A18" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A19" t="s">
-        <v>162</v>
-      </c>
-      <c r="B19" s="10">
-        <f>B11/$B$24</f>
-        <v>3333.3333333333335</v>
-      </c>
-      <c r="C19" s="10" t="str">
-        <f>TEXT(B19,"0.000000E+00")&amp;" "&amp;$A$30</f>
-        <v>3.333333E+03 Ns/mm</v>
-      </c>
-      <c r="E19" s="10">
-        <f>E11/$B$24</f>
-        <v>333333.33333333331</v>
-      </c>
-      <c r="F19" s="10" t="str">
-        <f>TEXT(E19,"0.000000E+00")&amp;" "&amp;$A$30</f>
-        <v>3.333333E+05 Ns/mm</v>
-      </c>
-      <c r="G19" s="10">
-        <f>G11/$B$24</f>
-        <v>3333333.3333333335</v>
-      </c>
-      <c r="H19" s="10" t="str">
-        <f>TEXT(G19,"0.000000E+00")&amp;" "&amp;$A$30</f>
-        <v>3.333333E+06 Ns/mm</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A20" t="s">
-        <v>166</v>
-      </c>
-      <c r="B20" s="10">
-        <f>B12*$B$25</f>
-        <v>58177.641733144323</v>
-      </c>
-      <c r="C20" s="10" t="str">
-        <f>TEXT(B20,"0.000000E+00")&amp;" "&amp;$A$31</f>
-        <v>5.817764E+04 Nms/°</v>
-      </c>
-      <c r="E20" s="10">
-        <f>E12*$B$25</f>
-        <v>5817764.1733144317</v>
-      </c>
-      <c r="F20" s="10" t="str">
-        <f>TEXT(E20,"0.000000E+00")&amp;" "&amp;$A$31</f>
-        <v>5.817764E+06 Nms/°</v>
-      </c>
-      <c r="G20" s="10">
-        <f>G12*$B$25</f>
-        <v>58177641.733144321</v>
-      </c>
-      <c r="H20" s="10" t="str">
-        <f>TEXT(G20,"0.000000E+00")&amp;" "&amp;$A$31</f>
-        <v>5.817764E+07 Nms/°</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A23" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A24" t="s">
-        <v>147</v>
-      </c>
-      <c r="B24" s="10">
-        <v>1000</v>
-      </c>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A25" t="s">
-        <v>148</v>
-      </c>
-      <c r="B25" s="10">
-        <f>PI()/180</f>
-        <v>1.7453292519943295E-2</v>
-      </c>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A27" s="6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A28" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A29" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A30" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A31" t="s">
-        <v>171</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="18"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
-  <ignoredErrors>
-    <ignoredError sqref="G19:G20" formula="1"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9938D174-4755-4D04-8086-39C09249D751}">
   <dimension ref="A1:S27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -3647,7 +3262,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B0B317E-EE6F-42FF-99F3-C97E08F0E85E}">
   <dimension ref="A1:G48"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -4256,4 +3871,389 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{718BB7D2-AA6F-42B4-9400-D5B966AA08E0}">
+  <dimension ref="A1:H31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="22.125" style="10" customWidth="1"/>
+    <col min="3" max="3" width="24.375" style="10" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="10" customWidth="1"/>
+    <col min="5" max="5" width="24.375" style="10" customWidth="1"/>
+    <col min="6" max="6" width="23.875" style="9" customWidth="1"/>
+    <col min="7" max="7" width="12.875" customWidth="1"/>
+    <col min="8" max="8" width="34" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="B1" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A2" s="6" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="10">
+        <v>1E-8</v>
+      </c>
+      <c r="E3" s="10">
+        <v>1E-10</v>
+      </c>
+      <c r="G3" s="10">
+        <v>9.9999999999999994E-12</v>
+      </c>
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="10">
+        <v>1E-8</v>
+      </c>
+      <c r="E4" s="10">
+        <v>1E-10</v>
+      </c>
+      <c r="G4" s="10">
+        <v>9.9999999999999994E-12</v>
+      </c>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" s="10">
+        <f>2/60</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="E5" s="10">
+        <f>2/60</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="G5" s="10">
+        <f>2/60</f>
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B8" s="10">
+        <f>1/B3</f>
+        <v>100000000</v>
+      </c>
+      <c r="E8" s="10">
+        <f>1/E3</f>
+        <v>10000000000</v>
+      </c>
+      <c r="G8" s="10">
+        <f>1/G3</f>
+        <v>100000000000</v>
+      </c>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B9" s="10">
+        <f>1/B4</f>
+        <v>100000000</v>
+      </c>
+      <c r="E9" s="10">
+        <f>1/E4</f>
+        <v>10000000000</v>
+      </c>
+      <c r="G9" s="10">
+        <f>1/G4</f>
+        <v>100000000000</v>
+      </c>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A10" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B11" s="10">
+        <f>B8*B5</f>
+        <v>3333333.3333333335</v>
+      </c>
+      <c r="E11" s="10">
+        <f>E8*E5</f>
+        <v>333333333.33333331</v>
+      </c>
+      <c r="G11" s="10">
+        <f>G8*G5</f>
+        <v>3333333333.3333335</v>
+      </c>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A12" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="10">
+        <f>B9*B5</f>
+        <v>3333333.3333333335</v>
+      </c>
+      <c r="E12" s="10">
+        <f>E9*E5</f>
+        <v>333333333.33333331</v>
+      </c>
+      <c r="G12" s="10">
+        <f>G9*G5</f>
+        <v>3333333333.3333335</v>
+      </c>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A14" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A15" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A16" t="s">
+        <v>160</v>
+      </c>
+      <c r="B16" s="10">
+        <f>B8/$B$24</f>
+        <v>100000</v>
+      </c>
+      <c r="C16" t="str">
+        <f>TEXT(B16,"0.000000E+00")&amp;" "&amp;$A$28</f>
+        <v>1.000000E+05 N/mm</v>
+      </c>
+      <c r="E16" s="10">
+        <f>E8/$B$24</f>
+        <v>10000000</v>
+      </c>
+      <c r="F16" t="str">
+        <f>TEXT(E16,"0.000000E+00")&amp;" "&amp;$A$28</f>
+        <v>1.000000E+07 N/mm</v>
+      </c>
+      <c r="G16" s="10">
+        <f>G8/$B$24</f>
+        <v>100000000</v>
+      </c>
+      <c r="H16" t="str">
+        <f>TEXT(G16,"0.000000E+00")&amp;" "&amp;$A$28</f>
+        <v>1.000000E+08 N/mm</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A17" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="10">
+        <f>B9*$B$25</f>
+        <v>1745329.2519943295</v>
+      </c>
+      <c r="C17" s="10" t="str">
+        <f>TEXT(B17,"0.000000E+00")&amp;" "&amp;$A$29</f>
+        <v>1.745329E+06 Nm/°</v>
+      </c>
+      <c r="E17" s="10">
+        <f>E9*$B$25</f>
+        <v>174532925.19943297</v>
+      </c>
+      <c r="F17" s="10" t="str">
+        <f>TEXT(E17,"0.000000E+00")&amp;" "&amp;$A$29</f>
+        <v>1.745329E+08 Nm/°</v>
+      </c>
+      <c r="G17" s="10">
+        <f>G9*$B$25</f>
+        <v>1745329251.9943295</v>
+      </c>
+      <c r="H17" s="10" t="str">
+        <f>TEXT(G17,"0.000000E+00")&amp;" "&amp;$A$29</f>
+        <v>1.745329E+09 Nm/°</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A18" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B19" s="10">
+        <f>B11/$B$24</f>
+        <v>3333.3333333333335</v>
+      </c>
+      <c r="C19" s="10" t="str">
+        <f>TEXT(B19,"0.000000E+00")&amp;" "&amp;$A$30</f>
+        <v>3.333333E+03 Ns/mm</v>
+      </c>
+      <c r="E19" s="10">
+        <f>E11/$B$24</f>
+        <v>333333.33333333331</v>
+      </c>
+      <c r="F19" s="10" t="str">
+        <f>TEXT(E19,"0.000000E+00")&amp;" "&amp;$A$30</f>
+        <v>3.333333E+05 Ns/mm</v>
+      </c>
+      <c r="G19" s="10">
+        <f>G11/$B$24</f>
+        <v>3333333.3333333335</v>
+      </c>
+      <c r="H19" s="10" t="str">
+        <f>TEXT(G19,"0.000000E+00")&amp;" "&amp;$A$30</f>
+        <v>3.333333E+06 Ns/mm</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A20" t="s">
+        <v>166</v>
+      </c>
+      <c r="B20" s="10">
+        <f>B12*$B$25</f>
+        <v>58177.641733144323</v>
+      </c>
+      <c r="C20" s="10" t="str">
+        <f>TEXT(B20,"0.000000E+00")&amp;" "&amp;$A$31</f>
+        <v>5.817764E+04 Nms/°</v>
+      </c>
+      <c r="E20" s="10">
+        <f>E12*$B$25</f>
+        <v>5817764.1733144317</v>
+      </c>
+      <c r="F20" s="10" t="str">
+        <f>TEXT(E20,"0.000000E+00")&amp;" "&amp;$A$31</f>
+        <v>5.817764E+06 Nms/°</v>
+      </c>
+      <c r="G20" s="10">
+        <f>G12*$B$25</f>
+        <v>58177641.733144321</v>
+      </c>
+      <c r="H20" s="10" t="str">
+        <f>TEXT(G20,"0.000000E+00")&amp;" "&amp;$A$31</f>
+        <v>5.817764E+07 Nms/°</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A23" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A24" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="10">
+        <v>1000</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A25" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="10">
+        <f>PI()/180</f>
+        <v>1.7453292519943295E-2</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A27" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A29" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A30" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A31" t="s">
+        <v>171</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="18"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="G19:G20" formula="1"/>
+  </ignoredErrors>
+</worksheet>
 </file>